--- a/songs/NoRoots_v1/quelle/struktur.xlsx
+++ b/songs/NoRoots_v1/quelle/struktur.xlsx
@@ -436,15 +436,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,6 +469,7 @@
       <c r="C2" s="2" t="n">
         <v>6</v>
       </c>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -478,6 +480,7 @@
       <c r="C3" s="2" t="n">
         <v>116</v>
       </c>
+      <c r="D3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -488,6 +491,7 @@
       <c r="C4" s="2" t="n">
         <v>0.25</v>
       </c>
+      <c r="D4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -502,20 +506,25 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Effektidee</t>
+          <t>Effekt (füllt KI)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Änderungswunsch</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -530,13 +539,19 @@
           <t>klick</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlack(6985, 1)   (Matrix: progScrollText("No Roots by Alice Merton", 15260, 75, getRandomColor(), 3))</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>progBlack(6985, 1)   (Matrix: progScrollText("No Roots by Alice Merton", 15260, 75, getRandomColor(), 3))</t>
         </is>
@@ -551,13 +566,19 @@
           <t>git</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(775, 2, 50, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>progStrobo(775, 2, 50, getRandomCRGB())</t>
         </is>
@@ -572,13 +593,19 @@
           <t>intro1</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(7500, 7, 3)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>progPalette(7500, 7, 3)</t>
         </is>
@@ -593,13 +620,19 @@
           <t>git</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(775, 4, 50, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>progStrobo(775, 4, 50, getRandomCRGB())</t>
         </is>
@@ -614,13 +647,19 @@
           <t>verse 1a</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(4135, 6, 5)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>progPalette(4135, 6, 5)</t>
         </is>
@@ -635,13 +674,19 @@
           <t>verse 1b</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(16555, 8, 6)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>progPalette(16555, 8, 6)</t>
         </is>
@@ -656,13 +701,19 @@
           <t>verse 1b</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progCircles(16550, 7, 260, false)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>progCircles(16550, 7, 260, false)</t>
         </is>
@@ -677,13 +728,19 @@
           <t>bridge</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progWaterRipple(7915, 8, 50, true, true)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(7915, 8, 50, true, true)</t>
         </is>
@@ -698,13 +755,19 @@
           <t>ROOTS 1</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1395, 9, 50, getRandomCRGB())   (Matrix: progShowROOTS(1395, 9))</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1395, 9, 50, getRandomCRGB())   (Matrix: progShowROOTS(1395, 9))</t>
         </is>
@@ -719,13 +782,19 @@
           <t>chorus a</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFullColors(2745, 10, 515)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>progFullColors(2745, 10, 515)</t>
         </is>
@@ -740,13 +809,19 @@
           <t>ROOTS 2</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1395, 11, 50, getRandomCRGB())   (Matrix: progShowROOTS(1395, 11))</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1395, 11, 50, getRandomCRGB())   (Matrix: progShowROOTS(1395, 11))</t>
         </is>
@@ -761,13 +836,19 @@
           <t>chorus a</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFullColors(3100, 12, 515)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>progFullColors(3100, 12, 515)</t>
         </is>
@@ -782,13 +863,19 @@
           <t>chorus rooooots</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(7750, 7, 13)</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(7750, 7, 13)</t>
         </is>
@@ -803,13 +890,19 @@
           <t>ROOTS 1</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1550, 14, 50, getRandomCRGB())   (Matrix: progShowROOTS(1550, 14))</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1550, 14, 50, getRandomCRGB())   (Matrix: progShowROOTS(1550, 14))</t>
         </is>
@@ -824,13 +917,19 @@
           <t>chorus a</t>
         </is>
       </c>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFullColors(2575, 15, 515)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>progFullColors(2575, 15, 515)</t>
         </is>
@@ -845,13 +944,19 @@
           <t>ROOTS 2</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1550, 16, 50, getRandomCRGB())   (Matrix: progShowROOTS(1550, 16))</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1550, 16, 50, getRandomCRGB())   (Matrix: progShowROOTS(1550, 16))</t>
         </is>
@@ -866,13 +971,19 @@
           <t>chorus a</t>
         </is>
       </c>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFullColors(3100, 18, 515)</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>progFullColors(3100, 18, 515)</t>
         </is>
@@ -887,13 +998,19 @@
           <t>chorus rooooots</t>
         </is>
       </c>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(8275, 7, 20)</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8275, 7, 20)</t>
         </is>
@@ -908,13 +1025,19 @@
           <t>verse 2a</t>
         </is>
       </c>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progWaterRipple(16550, 25, 50, true, true)</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(16550, 25, 50, true, true)</t>
         </is>
@@ -929,13 +1052,19 @@
           <t>verse 2b</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progCircles(16550, 27, 515)</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>progCircles(16550, 27, 515)</t>
         </is>
@@ -950,13 +1079,19 @@
           <t>bridge</t>
         </is>
       </c>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(7750, 4, 29)</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>progPalette(7750, 4, 29)</t>
         </is>
@@ -971,13 +1106,19 @@
           <t>ROOTS 1</t>
         </is>
       </c>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1550, 31, 50, getRandomCRGB())   (Matrix: progShowROOTS(1550, 31))</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1550, 31, 50, getRandomCRGB())   (Matrix: progShowROOTS(1550, 31))</t>
         </is>
@@ -992,13 +1133,19 @@
           <t>chorus a</t>
         </is>
       </c>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFullColors(2575, 33, 515)</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>progFullColors(2575, 33, 515)</t>
         </is>
@@ -1013,13 +1160,19 @@
           <t>ROOTS 2</t>
         </is>
       </c>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1550, 35, 50, getRandomCRGB())   (Matrix: progShowROOTS(1550, 35))</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1550, 35, 50, getRandomCRGB())   (Matrix: progShowROOTS(1550, 35))</t>
         </is>
@@ -1034,13 +1187,19 @@
           <t>chorus a</t>
         </is>
       </c>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFullColors(3100, 37, 515)</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>progFullColors(3100, 37, 515)</t>
         </is>
@@ -1055,13 +1214,19 @@
           <t>chorus rooooots</t>
         </is>
       </c>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(7750, 7, 39)</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(7750, 7, 39)</t>
         </is>
@@ -1076,13 +1241,19 @@
           <t>ROOTS 1</t>
         </is>
       </c>
-      <c r="C32" s="6" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1550, 41, 50, getRandomCRGB())   (Matrix: progShowROOTS(1550, 41))</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1550, 41, 50, getRandomCRGB())   (Matrix: progShowROOTS(1550, 41))</t>
         </is>
@@ -1097,13 +1268,19 @@
           <t>chorus a</t>
         </is>
       </c>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFullColors(2575, 43, 515)</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>progFullColors(2575, 43, 515)</t>
         </is>
@@ -1118,13 +1295,19 @@
           <t>ROOTS 2</t>
         </is>
       </c>
-      <c r="C34" s="6" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1550, 45, 50, getRandomCRGB())   (Matrix: progShowROOTS(1550, 45))</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1550, 45, 50, getRandomCRGB())   (Matrix: progShowROOTS(1550, 45))</t>
         </is>
@@ -1139,13 +1322,19 @@
           <t>chorus a</t>
         </is>
       </c>
-      <c r="C35" s="6" t="n"/>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFullColors(3100, 47, 515)</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
         <is>
           <t>progFullColors(3100, 47, 515)</t>
         </is>
@@ -1160,13 +1349,19 @@
           <t>chorus rooooots</t>
         </is>
       </c>
-      <c r="C36" s="6" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(8275, 7, 49)</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8275, 7, 49)</t>
         </is>
@@ -1181,13 +1376,19 @@
           <t>zwischenspiel</t>
         </is>
       </c>
-      <c r="C37" s="6" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+matrixMovieFX(18600, 51, 100, 6)</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
         <is>
           <t>matrixMovieFX(18600, 51, 100, 6)</t>
         </is>
@@ -1202,13 +1403,19 @@
           <t>solo</t>
         </is>
       </c>
-      <c r="C38" s="6" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F38" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progMatrixScanner(16550, 53, 15)</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(16550, 53, 15)</t>
         </is>
@@ -1223,13 +1430,19 @@
           <t>chorus</t>
         </is>
       </c>
-      <c r="C39" s="6" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(8275, 500, 55, 5, 26, 5, true, 3)</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(8275, 500, 55, 5, 26, 5, true, 3)</t>
         </is>
@@ -1244,13 +1457,19 @@
           <t>chorus</t>
         </is>
       </c>
-      <c r="C40" s="6" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F40" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(8275, 7, 57)</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8275, 7, 57)</t>
         </is>
@@ -1265,13 +1484,19 @@
           <t>chorus</t>
         </is>
       </c>
-      <c r="C41" s="6" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F41" s="6" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progWaterRipple(8275, 59, 50, true, false)</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(8275, 59, 50, true, false)</t>
         </is>
@@ -1286,13 +1511,19 @@
           <t>chorus</t>
         </is>
       </c>
-      <c r="C42" s="6" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F42" s="6" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(8275, 12, 61)</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8275, 12, 61)</t>
         </is>
@@ -1312,10 +1543,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="E43" t="n">
         <v>0</v>
       </c>
-      <c r="E43">
+      <c r="F43">
         <f>$C$3</f>
         <v/>
       </c>

--- a/songs/NoRoots_v1/quelle/struktur.xlsx
+++ b/songs/NoRoots_v1/quelle/struktur.xlsx
@@ -532,7 +532,7 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>3.625</v>
+        <v>4.625</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>7.625</v>
+        <v>8.625</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>29.825</v>
+        <v>30.825</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>30.5</v>
+        <v>31.5</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>31.825</v>
+        <v>32.825</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>32.5</v>
+        <v>33.5</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>37.75</v>
+        <v>38.75</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>38.5</v>
+        <v>39.5</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>39.75</v>
+        <v>40.75</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>40.5</v>
+        <v>41.5</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>65.75</v>
+        <v>66.75</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>66.5</v>
+        <v>67.5</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>67.75</v>
+        <v>68.75</v>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>68.5</v>
+        <v>69.5</v>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
-        <v>73.75</v>
+        <v>74.75</v>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
-        <v>74.5</v>
+        <v>75.5</v>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
-        <v>75.75</v>
+        <v>76.75</v>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
-        <v>76.5</v>
+        <v>77.5</v>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>

--- a/songs/NoRoots_v1/quelle/struktur.xlsx
+++ b/songs/NoRoots_v1/quelle/struktur.xlsx
@@ -436,16 +436,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,6 +471,7 @@
         <v>6</v>
       </c>
       <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -481,6 +483,7 @@
         <v>116</v>
       </c>
       <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -492,6 +495,7 @@
         <v>0.25</v>
       </c>
       <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -516,15 +520,20 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>Neuer Vorschlag (KI)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -546,12 +555,13 @@
         </is>
       </c>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>progBlack(6985, 1)   (Matrix: progScrollText("No Roots by Alice Merton", 15260, 75, getRandomColor(), 3))</t>
         </is>
@@ -573,12 +583,17 @@
         </is>
       </c>
       <c r="D7" s="6" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Strobo nur auf Gitarre und Bass (only guitar), Rest dunkel - der Gitarren-Einwurf. Gilt auch für "git (2)".</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>progStrobo(775, 2, 50, getRandomCRGB())</t>
         </is>
@@ -600,12 +615,17 @@
         </is>
       </c>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Szene Calm, SUNSET, weich eingeblendet (fade_in 2 Beats).</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>progPalette(7500, 7, 3)</t>
         </is>
@@ -627,12 +647,13 @@
         </is>
       </c>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>progStrobo(775, 4, 50, getRandomCRGB())</t>
         </is>
@@ -654,12 +675,13 @@
         </is>
       </c>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>progPalette(4135, 6, 5)</t>
         </is>
@@ -681,12 +703,17 @@
         </is>
       </c>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Szene Verse, SUNSET: dezenter Puls im Beat.</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>progPalette(16555, 8, 6)</t>
         </is>
@@ -708,12 +735,17 @@
         </is>
       </c>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Szene Call Response, SUNSET: Bühnenhälften blitzen abwechselnd - Steigerung.</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>progCircles(16550, 7, 260, false)</t>
         </is>
@@ -735,12 +767,17 @@
         </is>
       </c>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Wasserringe bleiben; in den letzten 2 Beats blendet ein Blinder ein, der genau auf dem ersten "ROOTS" voll ist (Takt 30,825).</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(7915, 8, 50, true, true)</t>
         </is>
@@ -762,12 +799,17 @@
         </is>
       </c>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Motiv bleibt: Strobo auf allen Geräten, "ROOTS" auf der Matrix - neu mit Farbverlauf in der Schrift und in Weiß statt Zufallsfarbe. Gilt für alle ROOTS 1 / ROOTS 2.</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1395, 9, 50, getRandomCRGB())   (Matrix: progShowROOTS(1395, 9))</t>
         </is>
@@ -789,12 +831,17 @@
         </is>
       </c>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Szene Colors, RETRO, soft 30: eine Farbe pro Beat auf der ganzen Bühne, mit kurzer Blende. Gilt für alle "chorus a".</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>progFullColors(2745, 10, 515)</t>
         </is>
@@ -816,12 +863,13 @@
         </is>
       </c>
       <c r="D16" s="6" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1395, 11, 50, getRandomCRGB())   (Matrix: progShowROOTS(1395, 11))</t>
         </is>
@@ -843,12 +891,13 @@
         </is>
       </c>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>progFullColors(3100, 12, 515)</t>
         </is>
@@ -870,12 +919,17 @@
         </is>
       </c>
       <c r="D18" s="6" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Szene Sparkle, RETRO (Einzelblitze wie bisher, in festen Farben). Gilt für alle "chorus rooooots".</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(7750, 7, 13)</t>
         </is>
@@ -897,12 +951,13 @@
         </is>
       </c>
       <c r="D19" s="6" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1550, 14, 50, getRandomCRGB())   (Matrix: progShowROOTS(1550, 14))</t>
         </is>
@@ -924,12 +979,13 @@
         </is>
       </c>
       <c r="D20" s="6" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>progFullColors(2575, 15, 515)</t>
         </is>
@@ -951,12 +1007,13 @@
         </is>
       </c>
       <c r="D21" s="6" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1550, 16, 50, getRandomCRGB())   (Matrix: progShowROOTS(1550, 16))</t>
         </is>
@@ -978,12 +1035,13 @@
         </is>
       </c>
       <c r="D22" s="6" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>progFullColors(3100, 18, 515)</t>
         </is>
@@ -1005,12 +1063,17 @@
         </is>
       </c>
       <c r="D23" s="6" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>wie oben; starker Blinder auf der letzten Viertel (Takt 46,75), danach weich in die Strophe (verse 2a mit Übergang fade, 4 Beats).</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8275, 7, 20)</t>
         </is>
@@ -1032,12 +1095,17 @@
         </is>
       </c>
       <c r="D24" s="6" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Szene Rain, SUNSET, Farbwanderung (triad, 2 Takte).</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(16550, 25, 50, true, true)</t>
         </is>
@@ -1059,12 +1127,17 @@
         </is>
       </c>
       <c r="D25" s="6" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Szene Verse, SUNSET (Kreise im Beat können auf der Matrix bleiben).</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>progCircles(16550, 27, 515)</t>
         </is>
@@ -1086,12 +1159,17 @@
         </is>
       </c>
       <c r="D26" s="6" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Szene Palette, SUNSET; in den letzten 2 Beats blendet der Blinder für "ROOTS" ein (voll auf Takt 66,75).</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>progPalette(7750, 4, 29)</t>
         </is>
@@ -1113,12 +1191,13 @@
         </is>
       </c>
       <c r="D27" s="6" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1550, 31, 50, getRandomCRGB())   (Matrix: progShowROOTS(1550, 31))</t>
         </is>
@@ -1140,12 +1219,13 @@
         </is>
       </c>
       <c r="D28" s="6" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>progFullColors(2575, 33, 515)</t>
         </is>
@@ -1167,12 +1247,13 @@
         </is>
       </c>
       <c r="D29" s="6" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1550, 35, 50, getRandomCRGB())   (Matrix: progShowROOTS(1550, 35))</t>
         </is>
@@ -1194,12 +1275,13 @@
         </is>
       </c>
       <c r="D30" s="6" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
         <is>
           <t>progFullColors(3100, 37, 515)</t>
         </is>
@@ -1221,12 +1303,13 @@
         </is>
       </c>
       <c r="D31" s="6" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(7750, 7, 39)</t>
         </is>
@@ -1248,12 +1331,13 @@
         </is>
       </c>
       <c r="D32" s="6" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1550, 41, 50, getRandomCRGB())   (Matrix: progShowROOTS(1550, 41))</t>
         </is>
@@ -1275,12 +1359,13 @@
         </is>
       </c>
       <c r="D33" s="6" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>progFullColors(2575, 43, 515)</t>
         </is>
@@ -1302,12 +1387,13 @@
         </is>
       </c>
       <c r="D34" s="6" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1550, 45, 50, getRandomCRGB())   (Matrix: progShowROOTS(1550, 45))</t>
         </is>
@@ -1329,12 +1415,13 @@
         </is>
       </c>
       <c r="D35" s="6" t="n"/>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
         <is>
           <t>progFullColors(3100, 47, 515)</t>
         </is>
@@ -1356,12 +1443,17 @@
         </is>
       </c>
       <c r="D36" s="6" t="n"/>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>wie oben; drei kurze Blinder am Ende (Takt 82,5 / 82,75 und die 1 von Takt 83).</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8275, 7, 49)</t>
         </is>
@@ -1383,12 +1475,17 @@
         </is>
       </c>
       <c r="D37" s="6" t="n"/>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Szene DNA Flip Scroll, ROYAL: Helix auf der Matrix, alle anderen pulsieren einmal je Takt - Farbwechsel ins Kühle als Kontrast (9 Takte).</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
         <is>
           <t>matrixMovieFX(18600, 51, 100, 6)</t>
         </is>
@@ -1410,12 +1507,17 @@
         </is>
       </c>
       <c r="D38" s="6" t="n"/>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>Szene Solo Gitarre (oder Solo Bass - wer spielt hier?), NEON: zwei Kometen um das Solo-Instrument, alle anderen atmen dunkel. Letzter Takt Szene Buildup (tail 4 Beats).</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(16550, 53, 15)</t>
         </is>
@@ -1437,12 +1539,17 @@
         </is>
       </c>
       <c r="D39" s="6" t="n"/>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>Stern bleibt, in RETRO, Blinder auf den Einsatz (2 Beats).</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(8275, 500, 55, 5, 26, 5, true, 3)</t>
         </is>
@@ -1464,12 +1571,13 @@
         </is>
       </c>
       <c r="D40" s="6" t="n"/>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8275, 7, 57)</t>
         </is>
@@ -1491,12 +1599,17 @@
         </is>
       </c>
       <c r="D41" s="6" t="n"/>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G41" s="6" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>Szene Fire, FIRE statt Wasserringe - der letzte Chorus soll nicht absacken.</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(8275, 59, 50, true, false)</t>
         </is>
@@ -1518,12 +1631,17 @@
         </is>
       </c>
       <c r="D42" s="6" t="n"/>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G42" s="6" t="inlineStr">
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>Szene Sparkle, FIRE; starker Blinder auf der letzten Viertel (Takt 115,75), klingt 5 Sekunden ins Schluss-Schwarz aus (wie APT.).</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8275, 12, 61)</t>
         </is>
@@ -1543,10 +1661,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
         <v>0</v>
       </c>
-      <c r="F43">
+      <c r="G43">
         <f>$C$3</f>
         <v/>
       </c>
